--- a/GREENBANK0_301A/project/Pre Hopper Run Checks.xlsx
+++ b/GREENBANK0_301A/project/Pre Hopper Run Checks.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="41">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -135,7 +135,10 @@
     <t>Missing Bio Symbol Files</t>
   </si>
   <si>
-    <t>No missing bio or symbol files...</t>
+    <t>PEBBLEtiehi.bio</t>
+  </si>
+  <si>
+    <t>PEBBLEtiehi.v</t>
   </si>
 </sst>
 </file>
@@ -746,7 +749,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -764,6 +767,11 @@
         <v>39</v>
       </c>
     </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/GREENBANK0_301A/project/Pre Hopper Run Checks.xlsx
+++ b/GREENBANK0_301A/project/Pre Hopper Run Checks.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="40">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -135,10 +135,7 @@
     <t>Missing Bio Symbol Files</t>
   </si>
   <si>
-    <t>PEBBLEtiehi.bio</t>
-  </si>
-  <si>
-    <t>PEBBLEtiehi.v</t>
+    <t>No missing bio or symbol files...</t>
   </si>
 </sst>
 </file>
@@ -749,7 +746,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -767,11 +764,6 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>40</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/GREENBANK0_301A/project/Pre Hopper Run Checks.xlsx
+++ b/GREENBANK0_301A/project/Pre Hopper Run Checks.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="41">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -79,6 +79,9 @@
   </si>
   <si>
     <t>Xdatamap4 (datamap.code) missing expected field datamap_code_2</t>
+  </si>
+  <si>
+    <t>XUSERVICEreference dftprobe_description total_bits:3 cannot be 'text'</t>
   </si>
   <si>
     <t>XU1,XceleraCORE,XU19</t>
@@ -501,7 +504,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A54"/>
+  <dimension ref="A1:A55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -590,12 +593,12 @@
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
         <v>22</v>
       </c>
     </row>
@@ -635,73 +638,73 @@
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>6</v>
+    <row r="31" spans="1:1">
+      <c r="A31" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" t="s">
-        <v>6</v>
+    <row r="36" spans="1:1">
+      <c r="A36" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
-      <c r="A40" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" t="s">
-        <v>6</v>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>22</v>
+    <row r="46" spans="1:1">
+      <c r="A46" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="48" spans="1:1">
@@ -721,7 +724,7 @@
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="52" spans="1:1">
@@ -737,6 +740,11 @@
     <row r="54" spans="1:1">
       <c r="A54" t="s">
         <v>37</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -751,7 +759,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -761,7 +769,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/GREENBANK0_301A/project/Pre Hopper Run Checks.xlsx
+++ b/GREENBANK0_301A/project/Pre Hopper Run Checks.xlsx
@@ -9,14 +9,13 @@
   <sheets>
     <sheet name="No Zero Net" sheetId="1" r:id="rId1"/>
     <sheet name="Validate no &quot;text&quot; in Datamaps" sheetId="2" r:id="rId2"/>
-    <sheet name="Missing Bio Symbol Files" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="39">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -133,12 +132,6 @@
   </si>
   <si>
     <t>Xdatamap1 (datamap.function) missing expected field datamap_function_7</t>
-  </si>
-  <si>
-    <t>Missing Bio Symbol Files</t>
-  </si>
-  <si>
-    <t>No missing bio or symbol files...</t>
   </si>
 </sst>
 </file>
@@ -750,29 +743,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>